--- a/FPS_Test/Assets/Excel/装備メモ/Book1.xlsx
+++ b/FPS_Test/Assets/Excel/装備メモ/Book1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\装備メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7073707-8961-4DA8-8133-834C29E4572F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AED900-B2FB-42E3-BB97-519E4612B2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" xr2:uid="{96C44E21-03A3-4D57-9AC6-6B37D672E1CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{96C44E21-03A3-4D57-9AC6-6B37D672E1CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="装備" sheetId="1" r:id="rId1"/>
+    <sheet name="武器" sheetId="2" r:id="rId2"/>
+    <sheet name="パッシブ" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
   <si>
     <t>MP</t>
     <phoneticPr fontId="1"/>
@@ -185,6 +186,234 @@
   </si>
   <si>
     <t>Lwand</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦士</t>
+    <rPh sb="0" eb="2">
+      <t>センシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法使い</t>
+    <rPh sb="0" eb="3">
+      <t>マホウツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>僧侶</t>
+    <rPh sb="0" eb="2">
+      <t>ソウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>盗賊</t>
+    <rPh sb="0" eb="2">
+      <t>トウゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてのステータスが少しだけ上昇する</t>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死に至る攻撃を一度だけ体力1で耐える</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の攻撃で受けるダメージをカットする</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃をした際に状態異常(やけど)をつけることがある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジョウタイイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃をした際に状態異常(凍傷)をつけることがある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジョウタイイジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃をした際に状態異常(感電)をつけることがある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジョウタイイジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンデン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徘徊するモンスターに与えるダメージが上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>ハイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体力が一定時間で自動回復する</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ジドウカイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム開始時に一定量のダメージから身を守るバリアを張る</t>
+    <rPh sb="3" eb="6">
+      <t>カイシジ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>イッテイリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>マモ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宝箱を開封するまでの時間が短くなる</t>
+    <rPh sb="0" eb="2">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイフウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミジカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度が少しだけ上昇する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Legendaryの宝箱を開けるカギを一つ所持する</t>
+    <rPh sb="10" eb="12">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>firstPassive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>secondPassive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ThirdPassive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jobName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jobType</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -520,7 +749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -586,6 +815,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1834,4 +2066,105 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE2134-888A-46D6-B8C0-DD699F9A1643}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="3" width="45.25" customWidth="1"/>
+    <col min="4" max="4" width="51" customWidth="1"/>
+    <col min="5" max="5" width="8.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/FPS_Test/Assets/Excel/装備メモ/Book1.xlsx
+++ b/FPS_Test/Assets/Excel/装備メモ/Book1.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\装備メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AED900-B2FB-42E3-BB97-519E4612B2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83B6DA1-E968-4A5F-8B01-B1949F34E666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{96C44E21-03A3-4D57-9AC6-6B37D672E1CD}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{96C44E21-03A3-4D57-9AC6-6B37D672E1CD}"/>
   </bookViews>
   <sheets>
     <sheet name="装備" sheetId="1" r:id="rId1"/>
     <sheet name="武器" sheetId="2" r:id="rId2"/>
-    <sheet name="パッシブ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>MP</t>
     <phoneticPr fontId="1"/>
@@ -189,231 +188,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>戦士</t>
+    <t>装備</t>
     <rPh sb="0" eb="2">
-      <t>センシ</t>
+      <t>ソウビ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔法使い</t>
-    <rPh sb="0" eb="3">
-      <t>マホウツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>僧侶</t>
-    <rPh sb="0" eb="2">
-      <t>ソウリョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>盗賊</t>
-    <rPh sb="0" eb="2">
-      <t>トウゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>すべてのステータスが少しだけ上昇する</t>
-    <rPh sb="10" eb="11">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死に至る攻撃を一度だけ体力1で耐える</t>
-    <rPh sb="0" eb="1">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>イタ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>タイリョク</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>相手の攻撃で受けるダメージをカットする</t>
-    <rPh sb="0" eb="2">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃をした際に状態異常(やけど)をつけることがある</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>ジョウタイイジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃をした際に状態異常(凍傷)をつけることがある</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>ジョウタイイジョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>トウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃をした際に状態異常(感電)をつけることがある</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>ジョウタイイジョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カンデン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>徘徊するモンスターに与えるダメージが上昇する</t>
-    <rPh sb="0" eb="2">
-      <t>ハイカイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>体力が一定時間で自動回復する</t>
-    <rPh sb="0" eb="2">
-      <t>タイリョク</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>イッテイジカン</t>
-    </rPh>
-    <rPh sb="8" eb="12">
-      <t>ジドウカイフク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲーム開始時に一定量のダメージから身を守るバリアを張る</t>
-    <rPh sb="3" eb="6">
-      <t>カイシジ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>イッテイリョウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>マモ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宝箱を開封するまでの時間が短くなる</t>
-    <rPh sb="0" eb="2">
-      <t>タカラバコ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カイフウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ミジカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動速度が少しだけ上昇する</t>
-    <rPh sb="0" eb="4">
-      <t>イドウソクド</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Legendaryの宝箱を開けるカギを一つ所持する</t>
-    <rPh sb="10" eb="12">
-      <t>タカラバコ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ショジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>firstPassive</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>secondPassive</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ThirdPassive</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>jobName</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>jobType</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -816,8 +594,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1133,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D3A7D3-4832-427A-B84B-CDABBCC2CCF5}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -1145,6 +923,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
       <c r="B1" t="s">
         <v>2</v>
       </c>
@@ -1179,22 +960,22 @@
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="6">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D2" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H2" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I2" s="6">
         <v>-5</v>
@@ -1209,22 +990,22 @@
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4">
         <v>10</v>
       </c>
       <c r="F3" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H3" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
@@ -1239,22 +1020,22 @@
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G4" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -1269,22 +1050,22 @@
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="11">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D5" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="11">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G5" s="11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H5" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="11">
         <v>0</v>
@@ -1299,22 +1080,22 @@
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="6">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E6" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G6" s="6">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H6" s="6">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I6" s="6">
         <v>-5</v>
@@ -1329,22 +1110,22 @@
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="4">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E7" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H7" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I7" s="4">
         <v>0</v>
@@ -1359,22 +1140,22 @@
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G8" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H8" s="4">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -1389,22 +1170,22 @@
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="11">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D9" s="11">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E9" s="11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F9" s="11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G9" s="11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H9" s="11">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I9" s="11">
         <v>5</v>
@@ -1419,22 +1200,22 @@
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="6">
+        <v>80</v>
+      </c>
+      <c r="D10" s="6">
+        <v>40</v>
+      </c>
+      <c r="E10" s="6">
         <v>20</v>
-      </c>
-      <c r="D10" s="6">
-        <v>25</v>
-      </c>
-      <c r="E10" s="6">
-        <v>40</v>
       </c>
       <c r="F10" s="6">
         <v>40</v>
       </c>
       <c r="G10" s="6">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H10" s="6">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I10" s="6">
         <v>-5</v>
@@ -1449,22 +1230,22 @@
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="4">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D11" s="4">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4">
         <v>20</v>
-      </c>
-      <c r="E11" s="4">
-        <v>30</v>
       </c>
       <c r="F11" s="4">
         <v>30</v>
       </c>
       <c r="G11" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H11" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
@@ -1479,22 +1260,22 @@
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4">
         <v>15</v>
       </c>
       <c r="G12" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H12" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -1509,10 +1290,10 @@
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="11">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D13" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E13" s="11">
         <v>20</v>
@@ -1521,10 +1302,10 @@
         <v>20</v>
       </c>
       <c r="G13" s="11">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H13" s="11">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I13" s="11">
         <v>10</v>
@@ -1532,6 +1313,198 @@
       <c r="J13" s="12">
         <v>0</v>
       </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1861,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E11" s="4">
         <v>20</v>
@@ -1891,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4">
         <v>30</v>
@@ -1921,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E13" s="11">
         <v>40</v>
@@ -2060,107 +2033,6 @@
       </c>
       <c r="J17" s="12">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE2134-888A-46D6-B8C0-DD699F9A1643}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="3" width="45.25" customWidth="1"/>
-    <col min="4" max="4" width="51" customWidth="1"/>
-    <col min="5" max="5" width="8.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
